--- a/samples/sujets.xlsx
+++ b/samples/sujets.xlsx
@@ -5,176 +5,353 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Consignes" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Reponses" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Sujet" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="52">
-  <si>
-    <t>Sujets Excel</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
+  <si>
+    <t>Étude de cas notée — Diagnostic d'un réseau de magasins</t>
+  </si>
+  <si>
+    <t>Analyse de données de ventes, de charges et de ressources humaines — durée conseillée : 120 min — noté sur 20 points</t>
+  </si>
+  <si>
+    <t>Contexte métier</t>
+  </si>
+  <si>
+    <t>Vous êtes analyste pour une enseigne de sneakers. Le PDG France martèle que les magasins qui vendent mal devraient « faire encore plus de promotions » pour relancer le chiffre d'affaires. Sur le terrain, les responsables défendent une autre lecture : organisation instable, manque de formation et turnover élevé des vendeurs. Personne n'a tranché avec des chiffres. À partir des fichiers fournis, vous devez (1) repérer le magasin réellement en difficulté, (2) tester les deux hypothèses avec des indicateurs, puis (3) conclure et proposer des actions. Le réseau compte plusieurs magasins : à vous d'identifier celui qui pose problème, on ne vous le donne pas.</t>
   </si>
   <si>
     <t>Fichiers de travail</t>
   </si>
   <si>
-    <t>ventes_exam.xlsx : 1 ligne = 1 ticket</t>
-  </si>
-  <si>
-    <t>store_month_costs.xlsx : charges par magasin-mois</t>
-  </si>
-  <si>
-    <t>magasins.xlsx : caracteristiques des magasins</t>
-  </si>
-  <si>
-    <t>Consigne</t>
-  </si>
-  <si>
-    <t>Renseignez vos resultats dans la feuille Reponses. La colonne Reponse est volontairement vide.</t>
-  </si>
-  <si>
-    <t>Vous pouvez utiliser SOMME.SI, MOYENNE.SI, NB.SI ou un tableau croise dynamique.</t>
-  </si>
-  <si>
-    <t>theme</t>
+    <t>ventes_exam.xlsx — 1 ligne = 1 ticket ; les colonnes produit sont répétées (product_1_*, product_2_*, …).</t>
+  </si>
+  <si>
+    <t>store_month_costs.xlsx — Charges et CA par magasin et par mois (12 mois par magasin).</t>
+  </si>
+  <si>
+    <t>magasins.xlsx — Caractéristiques des magasins (type, zone, surface…).</t>
+  </si>
+  <si>
+    <t>employes.xlsx — Vendeurs : ancienneté, dates d'embauche et de départ, magasin.</t>
+  </si>
+  <si>
+    <t>À retenir</t>
+  </si>
+  <si>
+    <t>Taux de TVA applicable : 20 %. TTC = HT × (1 + 0.2).</t>
+  </si>
+  <si>
+    <t>Séparateur décimal : la virgule. Séparateur de colonnes des CSV : le point-virgule.</t>
+  </si>
+  <si>
+    <t>Dans ventes_exam.xlsx, les colonnes sale_total_ht et sale_total_ttc sont VIDES : c'est à vous de les reconstruire.</t>
+  </si>
+  <si>
+    <t>Données de l'année civile : une embauche « en cours d'année » a une hire_date à partir du 1er janvier de l'année étudiée.</t>
+  </si>
+  <si>
+    <t>Consignes générales</t>
+  </si>
+  <si>
+    <t>Reportez chaque résultat dans la feuille « Sujet », colonne « reponse ».</t>
+  </si>
+  <si>
+    <t>Vous pouvez utiliser SOMME.SI / MOYENNE.SI / NB.SI / NB.SI.ENS ou un tableau croisé dynamique.</t>
+  </si>
+  <si>
+    <t>Arrondissez les montants à 2 décimales et les taux à 1 décimale.</t>
+  </si>
+  <si>
+    <t>Pour la question de synthèse, rédigez un paragraphe argumenté citant au moins trois indicateurs chiffrés.</t>
+  </si>
+  <si>
+    <t>Barème</t>
+  </si>
+  <si>
+    <t>Partie</t>
+  </si>
+  <si>
+    <t>Objectif</t>
+  </si>
+  <si>
+    <t>Points</t>
+  </si>
+  <si>
+    <t>Partie A — Indicateurs de vente</t>
+  </si>
+  <si>
+    <t>Prendre en main ventes_exam.xlsx et produire les agrégats de base.</t>
+  </si>
+  <si>
+    <t>Partie B — Performance des équipes de vente</t>
+  </si>
+  <si>
+    <t>Croiser ventes et vendeurs pour mesurer l'efficacité commerciale.</t>
+  </si>
+  <si>
+    <t>Partie C — Rentabilité et structure de coûts</t>
+  </si>
+  <si>
+    <t>Évaluer la rentabilité réelle et le poids des charges, magasin par magasin.</t>
+  </si>
+  <si>
+    <t>Partie D — Diagnostic RH et synthèse</t>
+  </si>
+  <si>
+    <t>Mesurer l'instabilité des équipes et trancher le débat métier.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>partie</t>
   </si>
   <si>
     <t>indicateur</t>
   </si>
   <si>
-    <t>question</t>
+    <t>enonce</t>
   </si>
   <si>
     <t>source</t>
   </si>
   <si>
+    <t>methode</t>
+  </si>
+  <si>
     <t>niveau</t>
   </si>
   <si>
+    <t>points</t>
+  </si>
+  <si>
     <t>reponse</t>
   </si>
   <si>
-    <t>Ventes</t>
-  </si>
-  <si>
-    <t>Panier moyen magasin</t>
-  </si>
-  <si>
-    <t>Calculez le panier moyen TTC par magasin a partir de ventes_exam.xlsx.</t>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Nombre de tickets par magasin</t>
+  </si>
+  <si>
+    <t>Comptez le nombre de tickets (lignes de ventes_exam) pour chaque magasin.</t>
   </si>
   <si>
     <t>ventes_exam.xlsx</t>
   </si>
   <si>
+    <t>NB.SI sur store_id, ou un tableau croisé dynamique (store_id en lignes, nombre de sale_id).</t>
+  </si>
+  <si>
     <t>facile</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Nombre de tickets magasin</t>
-  </si>
-  <si>
-    <t>Comptez le nombre de tickets par magasin.</t>
-  </si>
-  <si>
-    <t>CA TTC magasin</t>
-  </si>
-  <si>
-    <t>Calculez le chiffre d'affaires TTC par magasin.</t>
-  </si>
-  <si>
-    <t>Vendeur</t>
-  </si>
-  <si>
-    <t>Panier moyen vendeur</t>
-  </si>
-  <si>
-    <t>Calculez le panier moyen TTC par vendeur.</t>
-  </si>
-  <si>
-    <t>Indice de vente additionnelle</t>
-  </si>
-  <si>
-    <t>Calculez la part des tickets avec plus d'un article par vendeur ou par magasin.</t>
-  </si>
-  <si>
-    <t>moyen</t>
-  </si>
-  <si>
-    <t>Client</t>
-  </si>
-  <si>
-    <t>Frequence d'achat client</t>
-  </si>
-  <si>
-    <t>Comptez le nombre de tickets par client et identifiez les clients les plus fideles.</t>
-  </si>
-  <si>
-    <t>Produits</t>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires TTC par magasin</t>
+  </si>
+  <si>
+    <t>Reconstruisez le total de chaque ticket : sale_total_ht = somme des product_i_price_ht du ticket, puis sale_total_ttc = sale_total_ht × 1,20 (TVA 20 %). Additionnez ensuite le TTC par magasin.</t>
+  </si>
+  <si>
+    <t>SOMME des product_i_price_ht par ligne, ×1,20, puis SOMME.SI par store_id.</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Panier moyen TTC par magasin</t>
+  </si>
+  <si>
+    <t>Calculez le panier moyen TTC de chaque magasin (CA TTC du magasin ÷ nombre de tickets du magasin).</t>
+  </si>
+  <si>
+    <t>Réutilisez A1 (tickets) et A2 (CA TTC).</t>
+  </si>
+  <si>
+    <t>A4</t>
   </si>
   <si>
     <t>Nombre moyen d'articles par ticket</t>
   </si>
   <si>
-    <t>Calculez la moyenne de line_count sur l'ensemble des tickets.</t>
-  </si>
-  <si>
-    <t>Promotions</t>
-  </si>
-  <si>
-    <t>Remise moyenne par ticket</t>
-  </si>
-  <si>
-    <t>Calculez la remise moyenne par ticket a partir de sale_total_discount.</t>
-  </si>
-  <si>
-    <t>Saisonnalite</t>
-  </si>
-  <si>
-    <t>CA mensuel</t>
-  </si>
-  <si>
-    <t>Calculez le chiffre d'affaires TTC par mois pour observer la saisonnalite.</t>
-  </si>
-  <si>
-    <t>Rentabilite</t>
-  </si>
-  <si>
-    <t>Part des charges sur le CA</t>
-  </si>
-  <si>
-    <t>Comparez total_store_cost et ca_ttc par magasin-mois.</t>
+    <t>Calculez le nombre moyen d'articles par ticket sur l'ensemble du réseau (moyenne de la colonne article_count).</t>
+  </si>
+  <si>
+    <t>MOYENNE de article_count.</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Indice de vente additionnelle par magasin</t>
+  </si>
+  <si>
+    <t>Calculez, pour chaque magasin, la part des tickets comportant plus d'un article (article_count &gt; 1).</t>
+  </si>
+  <si>
+    <t>NB.SI.ENS (store_id et article_count&gt;1) ÷ nombre de tickets du magasin.</t>
+  </si>
+  <si>
+    <t>intermédiaire</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Panier moyen TTC par vendeur</t>
+  </si>
+  <si>
+    <t>Calculez le panier moyen TTC par vendeur (regroupement par employee_id), à partir du TTC reconstruit en A2.</t>
+  </si>
+  <si>
+    <t>Tableau croisé dynamique : employee_id en lignes, moyenne du TTC du ticket.</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>CA TTC par vendeur actif</t>
+  </si>
+  <si>
+    <t>Pour chaque magasin, divisez le CA TTC du magasin (A2) par le nombre de vendeurs ENCORE en poste (lignes de employes.xlsx dont end_date est vide). Comparez les magasins entre eux.</t>
+  </si>
+  <si>
+    <t>ventes_exam.xlsx + employes.xlsx</t>
+  </si>
+  <si>
+    <t>NB.SI.ENS sur employes (store_id, end_date vide) pour l'effectif actif, puis CA TTC ÷ effectif.</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>Taux de remise par magasin</t>
+  </si>
+  <si>
+    <t>Calculez le taux de remise moyen par magasin = somme(sale_total_discount) ÷ CA TTC du magasin (A2). Un magasin qui « fait beaucoup de promotions » aura un taux élevé.</t>
+  </si>
+  <si>
+    <t>SOMME.SI de sale_total_discount par store_id, divisé par le CA TTC du magasin.</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Résultat annuel par magasin</t>
+  </si>
+  <si>
+    <t>Pour chaque magasin, calculez le résultat annuel = somme(ca_ttc) − somme(total_store_cost) sur les 12 mois. Indiquez le(s) magasin(s) déficitaire(s).</t>
   </si>
   <si>
     <t>store_month_costs.xlsx</t>
   </si>
   <si>
+    <t>SOMME.SI de ca_ttc et de total_store_cost par store_id, puis différence.</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
     <t>Poids de la masse salariale</t>
   </si>
   <si>
-    <t>Calculez la part de gross_payroll + employer_contrib dans le total des charges.</t>
-  </si>
-  <si>
-    <t>Magasin</t>
-  </si>
-  <si>
-    <t>CA au m2</t>
-  </si>
-  <si>
-    <t>Calculez le chiffre d'affaires TTC par metre carre a partir de magasins.xlsx et store_month_costs.xlsx.</t>
-  </si>
-  <si>
-    <t>magasins.xlsx + store_month_costs.xlsx</t>
+    <t>Calculez la part de la masse salariale dans les charges = somme(gross_payroll + employer_contrib) ÷ somme(total_store_cost), par magasin.</t>
+  </si>
+  <si>
+    <t>SOMME.SI des trois colonnes par store_id, puis ratio.</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires au m²</t>
+  </si>
+  <si>
+    <t>Calculez le CA TTC annuel au mètre carré de chaque magasin = somme(ca_ttc) ÷ surface (issue de magasins.xlsx).</t>
+  </si>
+  <si>
+    <t>store_month_costs.xlsx + magasins.xlsx</t>
+  </si>
+  <si>
+    <t>RECHERCHEV de la surface dans magasins.xlsx, puis CA TTC ÷ surface.</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Effort promotionnel rapporté au CA</t>
+  </si>
+  <si>
+    <t>Calculez le taux d'effort marketing par magasin = somme(local_marketing) ÷ somme(ca_ttc). Cet indicateur teste directement l'hypothèse du PDG (« faire plus de promotions »).</t>
+  </si>
+  <si>
+    <t>SOMME.SI de local_marketing et de ca_ttc par store_id, puis ratio.</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Ancienneté moyenne des vendeurs</t>
+  </si>
+  <si>
+    <t>Calculez l'ancienneté moyenne (anciennete_mois) des vendeurs encore en poste, par magasin.</t>
+  </si>
+  <si>
+    <t>employes.xlsx</t>
+  </si>
+  <si>
+    <t>MOYENNE.SI.ENS de anciennete_mois (store_id, end_date vide).</t>
+  </si>
+  <si>
+    <t>avancé</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Taux de renouvellement de l'équipe</t>
+  </si>
+  <si>
+    <t>Pour chaque magasin, comptez (a) les départs (end_date renseignée) et (b) les embauches en cours d'année (hire_date à partir du 1er janvier de l'année étudiée). Rapportez ce total à l'effectif du magasin pour obtenir un taux de renouvellement.</t>
+  </si>
+  <si>
+    <t>NB.SI.ENS pour les départs et pour les embauches récentes, divisé par l'effectif total du magasin.</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Synthèse argumentée et recommandations</t>
+  </si>
+  <si>
+    <t>Le réseau compte plusieurs magasins déficitaires (C1) : leurs causes ne sont pas forcément les mêmes. Repérez celui dont la difficulté s'explique par l'INSTABILITÉ DE L'ÉQUIPE : ancienneté la plus faible (D1) et renouvellement le plus élevé (D2). Montrez ensuite que, pour ce magasin, le taux de remise (B4) et l'effort marketing (C4) ne sont PAS inférieurs aux autres — l'hypothèse « plus de promotions » du PDG n'explique donc pas sa contre-performance — alors que son CA par vendeur (B3) et son ancienneté (D1) révèlent le vrai problème. Citez au moins TROIS indicateurs chiffrés, concluez et proposez deux actions correctives.</t>
+  </si>
+  <si>
+    <t>toutes les parties précédentes</t>
+  </si>
+  <si>
+    <t>Réponse rédigée : comparer le magasin faible aux autres et montrer quelle hypothèse les données soutiennent.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -188,11 +365,20 @@
       <sz val="18"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF1E3A46"/>
+    </font>
+    <font>
       <b/>
+      <color rgb="FFD65A31"/>
+      <sz val="12"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFDF8EE"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="4">
@@ -240,18 +426,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -594,10 +782,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="24" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="5" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -609,44 +798,247 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="5" ht="112" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" ht="32" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="6">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="20">
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -655,279 +1047,485 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="58" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="4">
+        <v>2</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="4">
+        <v>2</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="C15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="C16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>19</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
